--- a/week-01/Ex5B Survey Results.xlsx
+++ b/week-01/Ex5B Survey Results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victoriaordonez\Documents\DataAnalytics\week-01\week-01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victoriaordonez\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{436A8AA9-28A6-40C6-92C7-44BFCB9D847A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
